--- a/data/Mar/11-03-2026/NGAY 11-3.xlsx
+++ b/data/Mar/11-03-2026/NGAY 11-3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\11-03-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\11-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5C77E2-CF97-4E2B-8007-16F1245CC3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21505C34-0AD2-4515-B52A-A6DE85FFD916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F8E69482-8B29-4E28-ACA9-4E97307A0D99}"/>
   </bookViews>
@@ -1219,95 +1219,109 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="2">
-        <v>230</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="2">
-        <v>10</v>
-      </c>
-      <c r="H3" s="2">
-        <v>715</v>
-      </c>
-      <c r="I3" s="2">
-        <v>25</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="C3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="3">
+        <v>440</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
         <f>H3-I3</f>
-        <v>690</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N3" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="R3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1690</v>
-      </c>
-      <c r="I4" s="2">
-        <v>30</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="C4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="3">
+        <v>490</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
         <f>H4-I4</f>
-        <v>1660</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M4" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
+      <c r="N4" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="R4" s="4">
         <v>1</v>
       </c>
@@ -1318,32 +1332,32 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4</v>
       </c>
       <c r="H5" s="2">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>25</v>
       </c>
       <c r="J5" s="2">
         <f>H5-I5</f>
-        <v>360</v>
+        <v>-25</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>109</v>
@@ -1360,48 +1374,50 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="35"/>
+      <c r="B6" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="C6" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="2">
-        <v>740</v>
-      </c>
-      <c r="I6" s="2">
-        <v>20</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="G6" s="35">
+        <v>7</v>
+      </c>
+      <c r="H6" s="35">
+        <v>130</v>
+      </c>
+      <c r="I6" s="35">
+        <v>30</v>
+      </c>
+      <c r="J6" s="35">
         <f>H6-I6</f>
-        <v>720</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="M6" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
+      <c r="N6" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
       <c r="R6">
         <v>1</v>
       </c>
@@ -1412,32 +1428,32 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>33</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10</v>
       </c>
       <c r="H7" s="2">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="I7" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J7" s="2">
         <f>H7-I7</f>
-        <v>-30</v>
+        <v>360</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>109</v>
@@ -1459,32 +1475,32 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="2">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H8" s="2">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="I8" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2">
         <f>H8-I8</f>
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>109</v>
@@ -1506,29 +1522,29 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="2">
-        <v>346</v>
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
+        <v>48</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="H9" s="2">
-        <v>605</v>
+        <v>395</v>
       </c>
       <c r="I9" s="2">
         <v>25</v>
       </c>
       <c r="J9" s="2">
         <f>H9-I9</f>
-        <v>580</v>
+        <v>370</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>120</v>
@@ -1553,32 +1569,32 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
+      </c>
+      <c r="E10" s="2">
+        <v>346</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4</v>
       </c>
       <c r="H10" s="2">
-        <v>815</v>
+        <v>605</v>
       </c>
       <c r="I10" s="2">
         <v>25</v>
       </c>
       <c r="J10" s="2">
         <f>H10-I10</f>
-        <v>790</v>
+        <v>580</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>109</v>
@@ -1600,32 +1616,32 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>87</v>
+      </c>
+      <c r="E11" s="2">
+        <v>230</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>56</v>
+        <v>88</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="I11" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J11" s="2">
         <f>H11-I11</f>
-        <v>-20</v>
+        <v>690</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>109</v>
@@ -1647,32 +1663,32 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="2">
-        <v>23</v>
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="2">
-        <v>7</v>
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H12" s="2">
-        <v>760</v>
+        <v>840</v>
       </c>
       <c r="I12" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2">
         <f>H12-I12</f>
-        <v>730</v>
+        <v>820</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>109</v>
@@ -1694,32 +1710,32 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>84</v>
+      </c>
+      <c r="E13" s="2">
+        <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
+      </c>
+      <c r="G13" s="2">
+        <v>7</v>
       </c>
       <c r="H13" s="2">
-        <v>395</v>
+        <v>760</v>
       </c>
       <c r="I13" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J13" s="2">
         <f>H13-I13</f>
-        <v>370</v>
+        <v>730</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>109</v>
@@ -1736,50 +1752,48 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="35">
-        <v>2</v>
-      </c>
-      <c r="H14" s="35">
-        <v>30</v>
-      </c>
-      <c r="I14" s="35">
-        <v>30</v>
-      </c>
-      <c r="J14" s="35">
+      <c r="C14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2">
+        <v>365</v>
+      </c>
+      <c r="I14" s="2">
+        <v>25</v>
+      </c>
+      <c r="J14" s="2">
         <f>H14-I14</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L14" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="M14" s="35" t="s">
+        <v>340</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="N14" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
       <c r="R14">
         <v>1</v>
       </c>
@@ -1790,32 +1804,32 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" s="2">
         <f>H15-I15</f>
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>109</v>
@@ -1832,87 +1846,81 @@
       </c>
     </row>
     <row r="16" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="3">
-        <v>490</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="2">
+        <v>710</v>
+      </c>
+      <c r="I16" s="2">
+        <v>30</v>
+      </c>
+      <c r="J16" s="2">
         <f>H16-I16</f>
-        <v>490</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="M16" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="N16" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
       <c r="R16" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>79</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2">
-        <v>710</v>
+        <v>7850</v>
       </c>
       <c r="I17" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J17" s="2">
         <f>H17-I17</f>
-        <v>680</v>
+        <v>7800</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>122</v>
@@ -1937,32 +1945,32 @@
         <v>19</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="G18" s="2">
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>840</v>
+        <v>1690</v>
       </c>
       <c r="I18" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J18" s="2">
         <f>H18-I18</f>
-        <v>820</v>
+        <v>1660</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>109</v>
@@ -1984,32 +1992,32 @@
         <v>19</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="G19" s="35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H19" s="35">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="I19" s="35">
         <v>30</v>
       </c>
       <c r="J19" s="35">
         <f>H19-I19</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K19" s="35" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L19" s="35" t="s">
         <v>109</v>
@@ -2033,29 +2041,29 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="2">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2">
-        <v>1565</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2">
         <f>H20-I20</f>
-        <v>1540</v>
+        <v>-20</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>109</v>
@@ -2080,32 +2088,32 @@
         <v>19</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>39</v>
+        <v>54</v>
+      </c>
+      <c r="E21" s="2">
+        <v>28</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H21" s="2">
-        <v>390</v>
+        <v>740</v>
       </c>
       <c r="I21" s="2">
         <v>20</v>
       </c>
       <c r="J21" s="2">
         <f>H21-I21</f>
-        <v>370</v>
+        <v>720</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>109</v>
@@ -2127,32 +2135,32 @@
         <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="2">
-        <v>213</v>
+        <v>62</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="2">
-        <v>9</v>
+        <v>64</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="H22" s="2">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="I22" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J22" s="2">
         <f>H22-I22</f>
         <v>790</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>109</v>
@@ -2174,19 +2182,19 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="2">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="H23" s="2">
         <v>385</v>
@@ -2199,7 +2207,7 @@
         <v>360</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>109</v>
@@ -2216,92 +2224,84 @@
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H24" s="3">
-        <v>440</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="C24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="2">
+        <v>49</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1565</v>
+      </c>
+      <c r="I24" s="2">
+        <v>25</v>
+      </c>
+      <c r="J24" s="2">
         <f>H24-I24</f>
-        <v>440</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N24" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>1540</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
       <c r="R24">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2">
+        <v>213</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>108</v>
+        <v>44</v>
+      </c>
+      <c r="G25" s="2">
+        <v>9</v>
       </c>
       <c r="H25" s="2">
-        <v>7850</v>
+        <v>820</v>
       </c>
       <c r="I25" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J25" s="2">
         <f>H25-I25</f>
-        <v>7800</v>
+        <v>790</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>109</v>
@@ -2699,8 +2699,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:Q25" xr:uid="{171E0929-AC05-4652-819E-FA7F40E9021D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q25">
-      <sortCondition ref="D2:D25"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:Q12">
+      <sortCondition ref="H2:H25"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">

--- a/data/Mar/11-03-2026/NGAY 11-3.xlsx
+++ b/data/Mar/11-03-2026/NGAY 11-3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\11-03-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\11-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21505C34-0AD2-4515-B52A-A6DE85FFD916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC73D1-1079-4798-96E3-D38C7EF50B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F8E69482-8B29-4E28-ACA9-4E97307A0D99}"/>
   </bookViews>
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3">
-        <f>H3-I3</f>
+        <f t="shared" ref="J3:J25" si="0">H3-I3</f>
         <v>440</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <f>H4-I4</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="K4" s="3" t="s">
@@ -1353,7 +1353,7 @@
         <v>25</v>
       </c>
       <c r="J5" s="2">
-        <f>H5-I5</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -1400,7 +1400,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="35">
-        <f>H6-I6</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="K6" s="35" t="s">
@@ -1449,7 +1449,7 @@
         <v>25</v>
       </c>
       <c r="J7" s="2">
-        <f>H7-I7</f>
+        <f t="shared" si="0"/>
         <v>360</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="2">
-        <f>H8-I8</f>
+        <f t="shared" si="0"/>
         <v>370</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -1543,7 +1543,7 @@
         <v>25</v>
       </c>
       <c r="J9" s="2">
-        <f>H9-I9</f>
+        <f t="shared" si="0"/>
         <v>370</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -1590,7 +1590,7 @@
         <v>25</v>
       </c>
       <c r="J10" s="2">
-        <f>H10-I10</f>
+        <f t="shared" si="0"/>
         <v>580</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -1637,7 +1637,7 @@
         <v>25</v>
       </c>
       <c r="J11" s="2">
-        <f>H11-I11</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -1684,7 +1684,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="2">
-        <f>H12-I12</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="K12" s="2" t="s">
@@ -1731,7 +1731,7 @@
         <v>30</v>
       </c>
       <c r="J13" s="2">
-        <f>H13-I13</f>
+        <f t="shared" si="0"/>
         <v>730</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -1778,7 +1778,7 @@
         <v>25</v>
       </c>
       <c r="J14" s="2">
-        <f>H14-I14</f>
+        <f t="shared" si="0"/>
         <v>340</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -1825,7 +1825,7 @@
         <v>30</v>
       </c>
       <c r="J15" s="2">
-        <f>H15-I15</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -1872,7 +1872,7 @@
         <v>30</v>
       </c>
       <c r="J16" s="2">
-        <f>H16-I16</f>
+        <f t="shared" si="0"/>
         <v>680</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -1919,7 +1919,7 @@
         <v>50</v>
       </c>
       <c r="J17" s="2">
-        <f>H17-I17</f>
+        <f t="shared" si="0"/>
         <v>7800</v>
       </c>
       <c r="K17" s="2" t="s">
@@ -1966,7 +1966,7 @@
         <v>30</v>
       </c>
       <c r="J18" s="2">
-        <f>H18-I18</f>
+        <f t="shared" si="0"/>
         <v>1660</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -2013,7 +2013,7 @@
         <v>30</v>
       </c>
       <c r="J19" s="35">
-        <f>H19-I19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19" s="35" t="s">
@@ -2062,7 +2062,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="2">
-        <f>H20-I20</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -2109,7 +2109,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="2">
-        <f>H21-I21</f>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -2156,7 +2156,7 @@
         <v>25</v>
       </c>
       <c r="J22" s="2">
-        <f>H22-I22</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="K22" s="2" t="s">
@@ -2203,7 +2203,7 @@
         <v>25</v>
       </c>
       <c r="J23" s="2">
-        <f>H23-I23</f>
+        <f t="shared" si="0"/>
         <v>360</v>
       </c>
       <c r="K23" s="2" t="s">
@@ -2250,7 +2250,7 @@
         <v>25</v>
       </c>
       <c r="J24" s="2">
-        <f>H24-I24</f>
+        <f t="shared" si="0"/>
         <v>1540</v>
       </c>
       <c r="K24" s="2" t="s">
@@ -2297,7 +2297,7 @@
         <v>30</v>
       </c>
       <c r="J25" s="2">
-        <f>H25-I25</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="K25" s="2" t="s">
@@ -2323,43 +2323,43 @@
         <v>20120</v>
       </c>
       <c r="I27">
-        <f t="shared" ref="I27:R27" si="0">SUBTOTAL(9,I3:I26)</f>
+        <f t="shared" ref="I27:R27" si="1">SUBTOTAL(9,I3:I26)</f>
         <v>565</v>
       </c>
       <c r="J27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19555</v>
       </c>
       <c r="K27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>4600</v>
       </c>
       <c r="N35" s="31">
-        <f t="shared" ref="N35" si="1">SUBTOTAL(9,N30:N34)</f>
+        <f t="shared" ref="N35" si="2">SUBTOTAL(9,N30:N34)</f>
         <v>7</v>
       </c>
       <c r="P35" s="32" t="s">
